--- a/lab3-buoi3_ktpm_quocphong_1150080153_11cnpm2.xlsx
+++ b/lab3-buoi3_ktpm_quocphong_1150080153_11cnpm2.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="681">
   <si>
     <t>Test case ID</t>
   </si>
@@ -3377,6 +3377,12 @@
   </si>
   <si>
     <t xml:space="preserve">Phân vùng tương đương </t>
+  </si>
+  <si>
+    <t>HỆ THỐNG HỖ TRỢ ĂN TRƯA CÁN BỘ</t>
+  </si>
+  <si>
+    <t>bonus</t>
   </si>
 </sst>
 </file>
@@ -9888,14 +9894,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="6">
-        <v>6</v>
+      <c r="A1" s="6" t="s">
+        <v>680</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>506</v>
+        <v>679</v>
       </c>
       <c r="D1" s="6"/>
       <c r="I1" s="13" t="s">

--- a/lab3-buoi3_ktpm_quocphong_1150080153_11cnpm2.xlsx
+++ b/lab3-buoi3_ktpm_quocphong_1150080153_11cnpm2.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="682">
   <si>
     <t>Test case ID</t>
   </si>
@@ -905,9 +905,6 @@
   </si>
   <si>
     <t>CỬA HÀNG BÁNH SINH NHẬT</t>
-  </si>
-  <si>
-    <t>Giá trị biên (Boundary Value Analysis)</t>
   </si>
   <si>
     <r>
@@ -1239,9 +1236,6 @@
     <t>CỬA HÀNG QUẦN ÁO</t>
   </si>
   <si>
-    <t>Phân vùng tương đương (Equivalence Partitioning)</t>
-  </si>
-  <si>
     <t>Điều kiện ưu đãi</t>
   </si>
   <si>
@@ -3319,9 +3313,6 @@
     <t>A5: Thông báo ngoài thời gian phục vụ</t>
   </si>
   <si>
-    <t>Bảng quyết định rút gọn (Decision Table)</t>
-  </si>
-  <si>
     <t>R6</t>
   </si>
   <si>
@@ -3383,6 +3374,18 @@
   </si>
   <si>
     <t>bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giá trị biên </t>
+  </si>
+  <si>
+    <t>Phân vùng tương đương</t>
+  </si>
+  <si>
+    <t>Giá trị biên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Điều kiện </t>
   </si>
 </sst>
 </file>
@@ -3466,7 +3469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3505,9 +3508,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="E1" s="6"/>
       <c r="I1" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -5804,7 +5804,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I3" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -5816,7 +5816,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I5" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -5842,7 +5842,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I7" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="E9" s="6"/>
       <c r="I9" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="E12" s="6"/>
       <c r="I12" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C14" s="13" t="s">
-        <v>286</v>
+        <v>678</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>261</v>
@@ -5919,10 +5919,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.35">
@@ -5930,51 +5930,51 @@
     </row>
     <row r="18" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C18" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="I18" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C19" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I19" s="15"/>
     </row>
     <row r="20" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C20" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="E20" s="2">
         <v>0.1</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.35">
@@ -5984,24 +5984,24 @@
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C23" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I23" s="15"/>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.35">
       <c r="I24" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C25" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>35</v>
@@ -6010,30 +6010,30 @@
     </row>
     <row r="26" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C26" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C27" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>35</v>
@@ -6042,76 +6042,76 @@
     </row>
     <row r="28" spans="3:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C28" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C29" s="14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C31" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I31" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="J31" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="K31" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="L31" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="M31" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="M31" s="4" t="s">
+      <c r="N31" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="32" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C32" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>276</v>
@@ -6131,19 +6131,19 @@
     </row>
     <row r="33" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C33" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>277</v>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="34" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I34" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>277</v>
@@ -6182,7 +6182,7 @@
       </c>
     </row>
     <row r="35" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I35" s="18" t="s">
+      <c r="I35" s="17" t="s">
         <v>275</v>
       </c>
       <c r="J35" s="4"/>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="36" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I36" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -6205,65 +6205,65 @@
     </row>
     <row r="37" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I37" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
     </row>
     <row r="38" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I38" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N38" s="4"/>
     </row>
     <row r="39" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I39" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" spans="3:14" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I42" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I44" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L44" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="45" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I45" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>276</v>
@@ -6275,12 +6275,12 @@
         <v>277</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I46" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>276</v>
@@ -6292,12 +6292,12 @@
         <v>276</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I47" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>277</v>
@@ -6309,12 +6309,12 @@
         <v>276</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="48" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="I48" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>277</v>
@@ -6326,12 +6326,12 @@
         <v>276</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I49" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>277</v>
@@ -6343,7 +6343,7 @@
         <v>277</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -6375,11 +6375,11 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E1" s="6"/>
       <c r="J1" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -6405,7 +6405,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J3" s="15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -6417,7 +6417,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J5" s="15" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -6443,7 +6443,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J7" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E9" s="6"/>
       <c r="J9" s="15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -6506,15 +6506,15 @@
     </row>
     <row r="14" spans="1:10" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C14" s="13" t="s">
-        <v>351</v>
+        <v>679</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C16" s="14" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>261</v>
@@ -6525,30 +6525,30 @@
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C18" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C19" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>272</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>35</v>
@@ -6557,30 +6557,30 @@
     </row>
     <row r="20" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C20" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C21" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>35</v>
@@ -6589,24 +6589,24 @@
     </row>
     <row r="22" spans="3:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C22" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="3:10" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C24" s="13" t="s">
-        <v>286</v>
+        <v>678</v>
       </c>
       <c r="J24" s="14" t="s">
         <v>275</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.35">
@@ -6628,169 +6628,169 @@
     </row>
     <row r="28" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C28" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="J28" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C29" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J29" s="15"/>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C30" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E30" s="2">
         <v>0.05</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C31" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E31" s="2">
         <v>0.1</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J31" s="15"/>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C32" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E32" s="2">
         <v>0.25</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C33" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="34" spans="3:14" ht="17.5" x14ac:dyDescent="0.35">
       <c r="J34" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="M36" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="N36" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="N36" s="3" t="s">
-        <v>335</v>
-      </c>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="K37" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L37" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N37" s="3" t="s">
+      <c r="L37" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N37" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.35">
+      <c r="J39" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L38" s="3" t="s">
+      <c r="K39" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M39" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M38" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="J39" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="N39" s="3" t="s">
+      <c r="N39" s="4" t="s">
         <v>277</v>
       </c>
     </row>
@@ -6798,78 +6798,78 @@
       <c r="J40" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="J41" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
+      <c r="J41" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
     </row>
     <row r="42" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="J42" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
+      <c r="J42" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
     </row>
     <row r="43" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="J43" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="N43" s="3"/>
+      <c r="J43" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="N43" s="4"/>
     </row>
     <row r="44" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="J44" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
+      <c r="J44" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
     </row>
     <row r="46" spans="3:14" ht="17.5" x14ac:dyDescent="0.35">
       <c r="J46" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="J48" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>272</v>
       </c>
       <c r="L48" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>356</v>
-      </c>
       <c r="N48" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49" spans="10:14" x14ac:dyDescent="0.35">
       <c r="J49" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>276</v>
@@ -6881,12 +6881,12 @@
         <v>277</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="10:14" ht="29" x14ac:dyDescent="0.35">
       <c r="J50" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>277</v>
@@ -6898,12 +6898,12 @@
         <v>277</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="10:14" ht="29" x14ac:dyDescent="0.35">
       <c r="J51" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>277</v>
@@ -6915,12 +6915,12 @@
         <v>276</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="10:14" ht="29" x14ac:dyDescent="0.35">
       <c r="J52" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>276</v>
@@ -6932,12 +6932,12 @@
         <v>277</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="10:14" ht="29" x14ac:dyDescent="0.35">
       <c r="J53" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>276</v>
@@ -6949,12 +6949,12 @@
         <v>276</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="10:14" ht="29" x14ac:dyDescent="0.35">
       <c r="J54" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>277</v>
@@ -6966,7 +6966,7 @@
         <v>277</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -6998,11 +6998,11 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E1" s="6"/>
       <c r="I1" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -7027,7 +7027,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -7039,7 +7039,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I5" s="15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -7065,7 +7065,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I7" s="15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="E9" s="6"/>
       <c r="I9" s="15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E11" s="6"/>
       <c r="I11" s="16" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -7133,38 +7133,38 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I13" s="15" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C14" s="13" t="s">
-        <v>351</v>
+        <v>675</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I15" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C16" s="14" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.35">
       <c r="I17" s="14" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C18" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>35</v>
@@ -7173,30 +7173,30 @@
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C19" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="C20" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>35</v>
@@ -7205,29 +7205,29 @@
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.35">
       <c r="I21" s="15" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C22" s="14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I22" s="15"/>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.35">
       <c r="I23" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C24" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>35</v>
@@ -7235,30 +7235,30 @@
     </row>
     <row r="25" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="C25" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="C26" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>35</v>
@@ -7267,19 +7267,19 @@
     </row>
     <row r="27" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="C27" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.35">
@@ -7287,10 +7287,10 @@
     </row>
     <row r="29" spans="3:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C29" s="13" t="s">
-        <v>286</v>
+        <v>680</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.35">
@@ -7298,180 +7298,180 @@
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="3:14" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C33" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C34" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C35" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E35" s="2">
         <v>0.1</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J35" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="M35" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="N35" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="36" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C36" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E36" s="2">
         <v>0.15</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J36" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N36" s="3" t="s">
+      <c r="L36" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N36" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C37" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E37" s="2">
         <v>0.2</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L37" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="M37" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="N37" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="38" spans="3:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C38" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E38" s="2">
         <v>0.3</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K38" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L38" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M38" s="3" t="s">
+      <c r="L38" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M38" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="N38" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="39" spans="3:14" ht="29" x14ac:dyDescent="0.35">
       <c r="C39" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>25</v>
@@ -7479,91 +7479,97 @@
       <c r="I39" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="6"/>
     </row>
     <row r="40" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="J40" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+    </row>
+    <row r="41" spans="3:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="I41" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+    </row>
+    <row r="42" spans="3:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="I42" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I41" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I42" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3" t="s">
-        <v>340</v>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I43" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="N43" s="3"/>
+      <c r="I43" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="N43" s="4"/>
     </row>
     <row r="44" spans="3:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="I44" s="3" t="s">
-        <v>294</v>
-      </c>
+      <c r="I44" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
     </row>
     <row r="46" spans="3:14" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I46" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="48" spans="3:14" x14ac:dyDescent="0.35">
       <c r="I48" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I49" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>276</v>
@@ -7575,12 +7581,12 @@
         <v>277</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I50" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>276</v>
@@ -7592,12 +7598,12 @@
         <v>276</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I51" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>277</v>
@@ -7609,12 +7615,12 @@
         <v>277</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I52" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>277</v>
@@ -7626,12 +7632,12 @@
         <v>276</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I53" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>277</v>
@@ -7643,12 +7649,12 @@
         <v>276</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="9:13" ht="29" x14ac:dyDescent="0.35">
       <c r="I54" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>277</v>
@@ -7660,7 +7666,7 @@
         <v>277</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -7688,11 +7694,11 @@
         <v>2</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D1" s="6"/>
       <c r="H1" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -7714,7 +7720,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -7723,7 +7729,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H5" s="15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -7746,7 +7752,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H7" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -7768,7 +7774,7 @@
       </c>
       <c r="D9" s="6"/>
       <c r="H9" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -7786,7 +7792,7 @@
       </c>
       <c r="D11" s="6"/>
       <c r="H11" s="15" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -7799,39 +7805,39 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H13" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
-        <v>351</v>
+        <v>675</v>
       </c>
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H15" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H17" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>35</v>
@@ -7839,30 +7845,30 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>422</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>35</v>
@@ -7871,19 +7877,19 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
@@ -7891,10 +7897,10 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B23" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
@@ -7902,30 +7908,30 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>35</v>
@@ -7934,19 +7940,19 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
@@ -7954,38 +7960,38 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>35</v>
@@ -7994,19 +8000,19 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.35">
@@ -8014,215 +8020,215 @@
     </row>
     <row r="35" spans="2:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B35" s="13" t="s">
-        <v>286</v>
+        <v>680</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="H36" s="15" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B38" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C38" s="3">
         <v>99</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="E38" s="19">
+        <v>469</v>
+      </c>
+      <c r="E38" s="18">
         <v>10</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C39" s="3">
         <v>100</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E39" s="19">
+        <v>471</v>
+      </c>
+      <c r="E39" s="18">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="29" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C40" s="3">
         <v>499</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="I40" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="K40" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="L40" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="M40" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C41" s="3">
         <v>500</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="E41" s="19">
+        <v>473</v>
+      </c>
+      <c r="E41" s="18">
         <v>0</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="I41" s="3" t="s">
+      <c r="H41" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M41" s="3" t="s">
+      <c r="J41" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M41" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="42" spans="2:13" ht="29" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C42" s="3">
         <v>501</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E42" s="19">
+        <v>367</v>
+      </c>
+      <c r="E42" s="18">
         <v>0</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J42" s="3" t="s">
+      <c r="H42" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J42" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="K42" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M42" s="3" t="s">
+      <c r="L42" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M42" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="H43" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K43" s="3" t="s">
+      <c r="H43" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K43" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M43" s="3" t="s">
+      <c r="L43" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="44" spans="2:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="H44" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L44" s="3" t="s">
+      <c r="H44" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="M44" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="H45" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M45" s="3" t="s">
+      <c r="H45" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M45" s="4" t="s">
         <v>276</v>
       </c>
     </row>
@@ -8230,76 +8236,77 @@
       <c r="H46" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="6"/>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="M47" s="3"/>
+      <c r="I47" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="M47" s="4"/>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="H48" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3" t="s">
-        <v>340</v>
+      <c r="H48" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H49" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
+      <c r="H49" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
     </row>
     <row r="51" spans="8:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H51" s="13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="53" spans="8:13" ht="29" x14ac:dyDescent="0.35">
       <c r="H53" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H54" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I54" s="3">
         <v>600</v>
@@ -8310,13 +8317,13 @@
       <c r="K54" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H55" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I55" s="3">
         <v>200</v>
@@ -8327,13 +8334,13 @@
       <c r="K55" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="18">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H56" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I56" s="3">
         <v>200</v>
@@ -8344,13 +8351,13 @@
       <c r="K56" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="57" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H57" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
@@ -8361,13 +8368,13 @@
       <c r="K57" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H58" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I58" s="3">
         <v>50</v>
@@ -8378,13 +8385,13 @@
       <c r="K58" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="59" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H59" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I59" s="3">
         <v>50</v>
@@ -8395,7 +8402,7 @@
       <c r="K59" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="18">
         <v>10</v>
       </c>
     </row>
@@ -8424,11 +8431,11 @@
         <v>2</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D1" s="6"/>
       <c r="H1" s="13" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -8450,44 +8457,44 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="H3" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="H4" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J4" s="3">
         <v>30</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="18">
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="H5" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J5" s="3">
         <v>22</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="18">
         <v>3000</v>
       </c>
     </row>
@@ -8508,29 +8515,29 @@
         <v>34</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J6" s="3">
         <v>40</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="18">
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="H7" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J7" s="3">
         <v>70</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="18">
         <v>1500</v>
       </c>
     </row>
@@ -8545,15 +8552,15 @@
         <v>11</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J8" s="3">
         <v>70</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="18">
         <v>1500</v>
       </c>
     </row>
@@ -8564,7 +8571,7 @@
       </c>
       <c r="D9" s="6"/>
       <c r="H9" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8582,7 +8589,7 @@
       </c>
       <c r="D11" s="6"/>
       <c r="H11" s="16" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8594,25 +8601,25 @@
     </row>
     <row r="13" spans="1:11" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H13" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
-        <v>351</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="H15" s="14" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>261</v>
@@ -8624,30 +8631,30 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>35</v>
@@ -8656,30 +8663,30 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>515</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>35</v>
@@ -8688,232 +8695,232 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H21" s="15" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
-        <v>286</v>
+        <v>680</v>
       </c>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H23" s="15" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H24" s="15"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C25" s="3">
         <v>24</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="E25" s="19">
+        <v>520</v>
+      </c>
+      <c r="E25" s="18">
         <v>3000</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C26" s="3">
         <v>25</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="E26" s="19">
+        <v>520</v>
+      </c>
+      <c r="E26" s="18">
         <v>1000</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C27" s="3">
         <v>64</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="E27" s="19">
+        <v>520</v>
+      </c>
+      <c r="E27" s="18">
         <v>1000</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C28" s="3">
         <v>65</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="E28" s="19">
+        <v>520</v>
+      </c>
+      <c r="E28" s="18">
         <v>1500</v>
       </c>
       <c r="H28" s="15"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C29" s="3">
         <v>64</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="E29" s="19">
+        <v>525</v>
+      </c>
+      <c r="E29" s="18">
         <v>500</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="E30" s="19">
+        <v>525</v>
+      </c>
+      <c r="E30" s="18">
         <v>1500</v>
       </c>
       <c r="H30" s="15"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H31" s="15" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H32" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="34" spans="8:12" x14ac:dyDescent="0.35">
       <c r="H34" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="36" spans="8:12" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H36" s="13" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="38" spans="8:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H38" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="H38" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="L38" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>430</v>
-      </c>
     </row>
     <row r="39" spans="8:12" x14ac:dyDescent="0.35">
-      <c r="H39" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="H39" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L39" s="3" t="s">
+      <c r="J39" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="40" spans="8:12" x14ac:dyDescent="0.35">
-      <c r="H40" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J40" s="3" t="s">
+      <c r="H40" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J40" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="K40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="41" spans="8:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H41" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K41" s="3" t="s">
+      <c r="H41" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K41" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="L41" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="42" spans="8:12" x14ac:dyDescent="0.35">
-      <c r="H42" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="H42" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>276</v>
       </c>
     </row>
@@ -8921,141 +8928,141 @@
       <c r="H43" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
     </row>
     <row r="44" spans="8:12" x14ac:dyDescent="0.35">
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+    </row>
+    <row r="45" spans="8:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H45" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+    </row>
+    <row r="46" spans="8:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H46" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="8:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H45" s="3" t="s">
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L46" s="4"/>
+    </row>
+    <row r="47" spans="8:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H47" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="8:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H46" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="8:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H47" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3" t="s">
-        <v>340</v>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H49" s="13" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H51" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H52" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J52" s="3">
         <v>30</v>
       </c>
-      <c r="K52" s="19">
+      <c r="K52" s="18">
         <v>500</v>
       </c>
     </row>
     <row r="53" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H53" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J53" s="3">
         <v>22</v>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="18">
         <v>3000</v>
       </c>
     </row>
     <row r="54" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H54" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J54" s="3">
         <v>40</v>
       </c>
-      <c r="K54" s="19">
+      <c r="K54" s="18">
         <v>1000</v>
       </c>
     </row>
     <row r="55" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H55" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J55" s="3">
         <v>70</v>
       </c>
-      <c r="K55" s="19">
+      <c r="K55" s="18">
         <v>1500</v>
       </c>
     </row>
     <row r="56" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H56" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J56" s="3">
         <v>70</v>
       </c>
-      <c r="K56" s="19">
+      <c r="K56" s="18">
         <v>1500</v>
       </c>
     </row>
@@ -9313,11 +9320,11 @@
         <v>2</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D1" s="6"/>
       <c r="G1" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -9339,7 +9346,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -9348,7 +9355,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G5" s="15" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -9371,7 +9378,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G7" s="15" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -9393,7 +9400,7 @@
       </c>
       <c r="D9" s="6"/>
       <c r="G9" s="15" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -9411,7 +9418,7 @@
       </c>
       <c r="D11" s="6"/>
       <c r="G11" s="15" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -9423,18 +9430,18 @@
     </row>
     <row r="14" spans="1:8" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
-        <v>351</v>
+        <v>679</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="14" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>422</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
@@ -9442,10 +9449,10 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>261</v>
@@ -9454,18 +9461,18 @@
         <v>35</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>554</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>35</v>
@@ -9474,19 +9481,19 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
@@ -9494,10 +9501,10 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" s="14" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.35">
@@ -9505,10 +9512,10 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>261</v>
@@ -9517,18 +9524,18 @@
         <v>35</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>35</v>
@@ -9536,19 +9543,19 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.35">
@@ -9556,10 +9563,10 @@
     </row>
     <row r="28" spans="2:8" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
-        <v>286</v>
+        <v>680</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
@@ -9567,27 +9574,27 @@
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="29" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C31" s="3">
         <v>20</v>
@@ -9596,16 +9603,16 @@
         <v>99</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H31" s="15"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C32" s="3">
         <v>20</v>
@@ -9614,18 +9621,18 @@
         <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C33" s="3">
         <v>21</v>
@@ -9634,16 +9641,16 @@
         <v>99</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H33" s="15"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C34" s="3">
         <v>21</v>
@@ -9652,18 +9659,18 @@
         <v>100</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C35" s="3">
         <v>22</v>
@@ -9672,65 +9679,65 @@
         <v>101</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H36" s="13" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H38" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="H38" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="L38" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>430</v>
-      </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="H39" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="H39" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K39" s="3" t="s">
+      <c r="J39" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K39" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="L39" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H40" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="H40" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="K40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>277</v>
       </c>
     </row>
@@ -9738,77 +9745,77 @@
       <c r="H41" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="H42" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="H42" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="H43" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="H43" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="H44" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L44" s="3"/>
+      <c r="H44" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" spans="2:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H45" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3" t="s">
-        <v>340</v>
+      <c r="H45" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="2:12" ht="17.5" x14ac:dyDescent="0.35">
       <c r="H47" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="49" spans="8:11" ht="29" x14ac:dyDescent="0.35">
       <c r="H49" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H50" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I50" s="3">
         <v>25</v>
@@ -9817,12 +9824,12 @@
         <v>200</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="51" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H51" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I51" s="3">
         <v>18</v>
@@ -9831,12 +9838,12 @@
         <v>150</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="52" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H52" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I52" s="3">
         <v>30</v>
@@ -9845,12 +9852,12 @@
         <v>50</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53" spans="8:11" ht="29" x14ac:dyDescent="0.35">
       <c r="H53" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="I53" s="3">
         <v>18</v>
@@ -9859,12 +9866,12 @@
         <v>50</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="54" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H54" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I54" s="3">
         <v>21</v>
@@ -9873,7 +9880,7 @@
         <v>100</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -9895,17 +9902,17 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D1" s="6"/>
       <c r="I1" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -9927,7 +9934,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -9935,7 +9942,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I5" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -9958,7 +9965,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I7" s="16" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -9980,7 +9987,7 @@
       </c>
       <c r="D9" s="6"/>
       <c r="I9" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -10005,76 +10012,76 @@
         <v>4</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="I12" s="20"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I13" s="20" t="s">
-        <v>643</v>
+      <c r="I13" s="19" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B14" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="I14" s="20"/>
+        <v>675</v>
+      </c>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I15" s="21" t="s">
-        <v>644</v>
+      <c r="I15" s="20" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="I16" s="20"/>
+        <v>597</v>
+      </c>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="I17" s="21" t="s">
-        <v>645</v>
+      <c r="I17" s="20" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="20"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>602</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="21" t="s">
-        <v>646</v>
+      <c r="I19" s="20" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -10082,28 +10089,28 @@
     </row>
     <row r="21" spans="2:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I21" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" s="14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="I23" s="22" t="s">
-        <v>422</v>
+      <c r="I23" s="21" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>35</v>
@@ -10112,30 +10119,30 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>612</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>35</v>
@@ -10144,19 +10151,19 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -10164,10 +10171,10 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B29" s="14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.35">
@@ -10175,30 +10182,30 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>618</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>35</v>
@@ -10207,30 +10214,30 @@
     </row>
     <row r="33" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>624</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>25</v>
@@ -10239,19 +10246,19 @@
     </row>
     <row r="35" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
@@ -10259,18 +10266,18 @@
     </row>
     <row r="37" spans="2:9" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B37" s="13" t="s">
-        <v>286</v>
+        <v>678</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>628</v>
-      </c>
-      <c r="I39" s="22" t="s">
-        <v>425</v>
+        <v>626</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.35">
@@ -10278,27 +10285,27 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C42" s="3">
         <v>100</v>
@@ -10307,16 +10314,16 @@
         <v>110</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="I42" s="15"/>
     </row>
     <row r="43" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C43" s="3">
         <v>100</v>
@@ -10325,18 +10332,18 @@
         <v>111</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C44" s="3">
         <v>50</v>
@@ -10345,16 +10352,16 @@
         <v>55</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="I44" s="15"/>
     </row>
     <row r="45" spans="2:9" ht="29" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C45" s="3">
         <v>50</v>
@@ -10363,13 +10370,13 @@
         <v>56</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.35">
@@ -10377,7 +10384,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.35">
       <c r="I47" s="15" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.35">
@@ -10385,195 +10392,195 @@
     </row>
     <row r="49" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I49" s="15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="51" spans="9:15" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I51" s="13" t="s">
-        <v>659</v>
+        <v>424</v>
       </c>
     </row>
     <row r="53" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I53" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J53" s="3" t="s">
+      <c r="I53" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="M53" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="N53" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="M53" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>660</v>
+      <c r="O53" s="4" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="54" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I54" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="J54" s="3" t="s">
+      <c r="I54" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="J54" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="K54" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L54" s="3" t="s">
+      <c r="L54" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="M54" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O54" s="3" t="s">
+      <c r="N54" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="O54" s="4" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="55" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I55" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="J55" s="3" t="s">
+      <c r="I55" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K55" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M55" s="3" t="s">
+      <c r="K55" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M55" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="N55" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O55" s="3" t="s">
+      <c r="N55" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="O55" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="56" spans="9:15" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="I56" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K56" s="3" t="s">
+      <c r="I56" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K56" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O56" s="3" t="s">
+      <c r="L56" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="O56" s="4" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="57" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I57" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L57" s="3" t="s">
+      <c r="I57" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L57" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O57" s="3" t="s">
+      <c r="M57" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="O57" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="58" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I58" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="J58" s="3" t="s">
+      <c r="I58" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="J58" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K58" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="L58" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O58" s="3" t="s">
+      <c r="M58" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="O58" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="59" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I59" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M59" s="3" t="s">
+      <c r="I59" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M59" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O59" s="3" t="s">
+      <c r="N59" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="O59" s="4" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="60" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I60" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O60" s="3" t="s">
+      <c r="I60" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="O60" s="4" t="s">
         <v>277</v>
       </c>
     </row>
@@ -10581,111 +10588,111 @@
       <c r="I61" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
     </row>
     <row r="62" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I62" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
+      <c r="I62" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
     </row>
     <row r="63" spans="9:15" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="I63" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3" t="s">
-        <v>340</v>
+      <c r="I63" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="9:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I64" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="O64" s="3"/>
+      <c r="I64" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="O64" s="4"/>
     </row>
     <row r="65" spans="9:15" x14ac:dyDescent="0.35">
-      <c r="I65" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="O65" s="3"/>
+      <c r="I65" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="O65" s="4"/>
     </row>
     <row r="67" spans="9:15" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I67" s="13" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="69" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I69" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="M69" s="2">
         <v>0.1</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="70" spans="9:15" ht="29" x14ac:dyDescent="0.35">
       <c r="I70" s="3" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>276</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M70" s="3" t="s">
         <v>277</v>
@@ -10694,21 +10701,21 @@
         <v>277</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="71" spans="9:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="I71" s="3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>276</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>277</v>
@@ -10717,21 +10724,21 @@
         <v>277</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="72" spans="9:15" ht="29" x14ac:dyDescent="0.35">
       <c r="I72" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>276</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>277</v>
@@ -10740,21 +10747,21 @@
         <v>277</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="73" spans="9:15" ht="29" x14ac:dyDescent="0.35">
       <c r="I73" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>276</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>276</v>
@@ -10763,44 +10770,44 @@
         <v>277</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="74" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I74" s="3" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>277</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="75" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I75" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>276</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M75" s="3" t="s">
         <v>277</v>
@@ -10809,7 +10816,7 @@
         <v>276</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
